--- a/Tests/Validation/Canola/Harden1999.xlsx
+++ b/Tests/Validation/Canola/Harden1999.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lil026\ApsimX\Prototypes\Canola\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\ApsimX\Tests\Validation\Canola\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACF9C78F-58F2-4057-9D5C-342C87D52CB4}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F4D98F2-1BFF-4783-910B-7E1F938BBBCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DCD4BBDB-2039-4016-B509-C04A516B8513}"/>
+    <workbookView xWindow="-27675" yWindow="1125" windowWidth="21600" windowHeight="11280" xr2:uid="{DCD4BBDB-2039-4016-B509-C04A516B8513}"/>
   </bookViews>
   <sheets>
     <sheet name="Observed" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="32">
   <si>
     <t>Canola.Density</t>
   </si>
@@ -74,12 +74,6 @@
     <t>Canola.Leaf.Dead.Wt</t>
   </si>
   <si>
-    <t>Canola.Grain.Nconc</t>
-  </si>
-  <si>
-    <t>Canola.Leaf.Live.Nconc</t>
-  </si>
-  <si>
     <t>treat</t>
   </si>
   <si>
@@ -101,12 +95,6 @@
     <t>Canola.Stage</t>
   </si>
   <si>
-    <t>Canola.Stem.Nconc</t>
-  </si>
-  <si>
-    <t>Canola.Pod.Nconc</t>
-  </si>
-  <si>
     <t>Canola.AboveGround.WtError</t>
   </si>
   <si>
@@ -132,6 +120,18 @@
   </si>
   <si>
     <t>Canola.DaysAfterSowing</t>
+  </si>
+  <si>
+    <t>Canola.Grain.NConc</t>
+  </si>
+  <si>
+    <t>Canola.Leaf.Live.NConc</t>
+  </si>
+  <si>
+    <t>Canola.Stem.NConc</t>
+  </si>
+  <si>
+    <t>Canola.Pod.NConc</t>
   </si>
 </sst>
 </file>
@@ -193,7 +193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -201,26 +201,14 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -239,9 +227,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -279,7 +267,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -385,7 +373,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -527,7 +515,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -551,7 +539,7 @@
     <col min="12" max="12" width="25.28515625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="28" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.7109375" style="22" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="23" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="21.7109375" bestFit="1" customWidth="1"/>
@@ -565,10 +553,10 @@
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C1" t="s">
         <v>3</v>
@@ -577,19 +565,19 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H1" t="s">
         <v>1</v>
       </c>
       <c r="I1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J1" t="s">
         <v>8</v>
@@ -604,49 +592,49 @@
         <v>10</v>
       </c>
       <c r="N1" t="s">
-        <v>16</v>
-      </c>
-      <c r="O1" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="O1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>30</v>
+      </c>
+      <c r="R1" t="s">
+        <v>31</v>
+      </c>
+      <c r="S1" t="s">
+        <v>28</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="P1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q1" t="s">
+      <c r="V1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="R1" t="s">
+      <c r="W1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="S1" t="s">
-        <v>12</v>
-      </c>
-      <c r="T1" s="5" t="s">
+      <c r="X1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="Y1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="Z1" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="W1" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="X1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z1" s="5" t="s">
-        <v>29</v>
       </c>
       <c r="AA1" t="s">
         <v>0</v>
       </c>
       <c r="AB1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
@@ -659,10 +647,10 @@
       <c r="C2" s="1">
         <v>36298</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="14">
         <v>36361</v>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="5">
         <f>D2-C2</f>
         <v>63</v>
       </c>
@@ -685,7 +673,7 @@
       <c r="N2" s="6">
         <v>0.25297144457579934</v>
       </c>
-      <c r="O2" s="23"/>
+      <c r="O2" s="5"/>
       <c r="P2" s="6">
         <v>6.31</v>
       </c>
@@ -734,11 +722,11 @@
       <c r="C3" s="1">
         <v>36298</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="14">
         <v>36398</v>
       </c>
-      <c r="E3" s="21">
-        <f t="shared" ref="E3:E66" si="0">D3-C3</f>
+      <c r="E3" s="5">
+        <f t="shared" ref="E3:E9" si="0">D3-C3</f>
         <v>100</v>
       </c>
       <c r="F3" t="s">
@@ -760,7 +748,7 @@
       <c r="N3" s="6">
         <v>1.7329083333333333</v>
       </c>
-      <c r="O3" s="23"/>
+      <c r="O3" s="5"/>
       <c r="P3" s="6">
         <v>5.18</v>
       </c>
@@ -809,10 +797,10 @@
       <c r="C4" s="1">
         <v>36298</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="14">
         <v>36412</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="5">
         <f t="shared" si="0"/>
         <v>114</v>
       </c>
@@ -834,7 +822,7 @@
       <c r="N4" s="6">
         <v>2.3277906508551722</v>
       </c>
-      <c r="O4" s="23">
+      <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="6">
@@ -885,10 +873,10 @@
       <c r="C5" s="1">
         <v>36298</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="14">
         <v>36431</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="5">
         <f t="shared" si="0"/>
         <v>133</v>
       </c>
@@ -914,7 +902,7 @@
       <c r="N5" s="6">
         <v>2.4512821035887336</v>
       </c>
-      <c r="O5" s="23"/>
+      <c r="O5" s="5"/>
       <c r="P5" s="6">
         <v>5.0199999999999996</v>
       </c>
@@ -965,10 +953,10 @@
       <c r="C6" s="1">
         <v>36298</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="14">
         <v>36445</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="5">
         <f t="shared" si="0"/>
         <v>147</v>
       </c>
@@ -994,7 +982,7 @@
       <c r="N6" s="6">
         <v>1.1765161313553172</v>
       </c>
-      <c r="O6" s="23"/>
+      <c r="O6" s="5"/>
       <c r="P6" s="6">
         <v>4.33</v>
       </c>
@@ -1008,9 +996,7 @@
       <c r="T6" s="5">
         <v>33.347144673772313</v>
       </c>
-      <c r="U6" s="5" t="s">
-        <v>2</v>
-      </c>
+      <c r="U6" s="5"/>
       <c r="V6" s="5">
         <v>7.9994730161642149</v>
       </c>
@@ -1045,10 +1031,10 @@
       <c r="C7" s="1">
         <v>36298</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="14">
         <v>36459</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="5">
         <f t="shared" si="0"/>
         <v>161</v>
       </c>
@@ -1074,7 +1060,7 @@
       <c r="N7" s="6">
         <v>1.2712457916798832</v>
       </c>
-      <c r="O7" s="23"/>
+      <c r="O7" s="5"/>
       <c r="P7" s="6">
         <v>4.29</v>
       </c>
@@ -1125,10 +1111,10 @@
       <c r="C8" s="1">
         <v>36298</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="14">
         <v>36473</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="5">
         <f t="shared" si="0"/>
         <v>175</v>
       </c>
@@ -1154,7 +1140,7 @@
       <c r="N8" s="6">
         <v>0.83799005345431432</v>
       </c>
-      <c r="O8" s="23"/>
+      <c r="O8" s="5"/>
       <c r="P8" s="6"/>
       <c r="Q8" s="6"/>
       <c r="R8" s="6">
@@ -1201,10 +1187,10 @@
       <c r="C9" s="1">
         <v>36298</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="14">
         <v>36487</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="5">
         <f t="shared" si="0"/>
         <v>189</v>
       </c>
@@ -1230,7 +1216,7 @@
         <v>284.99444444444447</v>
       </c>
       <c r="N9" s="6"/>
-      <c r="O9" s="23">
+      <c r="O9" s="5">
         <v>9</v>
       </c>
       <c r="P9" s="6"/>
@@ -1273,139 +1259,136 @@
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.25">
       <c r="C10" s="1"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="21"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="5"/>
       <c r="I10" s="6"/>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.25">
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
-      <c r="E11" s="21"/>
-    </row>
-    <row r="12" spans="1:34" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="21"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="24"/>
-      <c r="P12" s="10"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-    </row>
-    <row r="13" spans="1:34" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="21"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="24"/>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-    </row>
-    <row r="14" spans="1:34" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="25"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="16"/>
-      <c r="S14" s="16"/>
-      <c r="T14" s="12"/>
-    </row>
-    <row r="15" spans="1:34" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="26"/>
-      <c r="P15" s="18"/>
-      <c r="Q15" s="18"/>
-      <c r="R15" s="18"/>
-      <c r="S15" s="18"/>
-      <c r="T15" s="12"/>
-    </row>
-    <row r="16" spans="1:34" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="17"/>
-      <c r="N16" s="17"/>
-      <c r="O16" s="26"/>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="17"/>
-      <c r="R16" s="17"/>
-      <c r="S16" s="17"/>
-      <c r="T16" s="12"/>
-    </row>
-    <row r="17" spans="3:19" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C17" s="8"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="21"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="24"/>
-      <c r="P17" s="10"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="11"/>
-      <c r="S17" s="11"/>
+      <c r="E11" s="5"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="5"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="5"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="4"/>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="11"/>
+      <c r="T14" s="7"/>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12"/>
+      <c r="P15" s="13"/>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13"/>
+      <c r="S15" s="13"/>
+      <c r="T15" s="7"/>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="12"/>
+      <c r="P16" s="12"/>
+      <c r="Q16" s="12"/>
+      <c r="R16" s="12"/>
+      <c r="S16" s="12"/>
+      <c r="T16" s="7"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C17" s="1"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="5"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="4"/>
     </row>
     <row r="18" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C18" s="1"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="21"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="5"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="3"/>
@@ -1421,8 +1404,8 @@
     </row>
     <row r="19" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C19" s="1"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="21"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="5"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="3"/>
@@ -1438,8 +1421,8 @@
     </row>
     <row r="20" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C20" s="1"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="21"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="5"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="3"/>
@@ -1455,8 +1438,8 @@
     </row>
     <row r="21" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C21" s="1"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="21"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="5"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="3"/>
@@ -1472,8 +1455,8 @@
     </row>
     <row r="22" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C22" s="1"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="21"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="5"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="3"/>
@@ -1489,8 +1472,8 @@
     </row>
     <row r="23" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C23" s="1"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="21"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="5"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="3"/>
@@ -1507,7 +1490,7 @@
     <row r="24" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
-      <c r="E24" s="21"/>
+      <c r="E24" s="5"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="3"/>
@@ -1524,7 +1507,7 @@
     <row r="25" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
-      <c r="E25" s="21"/>
+      <c r="E25" s="5"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="3"/>
@@ -1541,7 +1524,7 @@
     <row r="26" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
-      <c r="E26" s="21"/>
+      <c r="E26" s="5"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="3"/>
@@ -1558,7 +1541,7 @@
     <row r="27" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
-      <c r="E27" s="21"/>
+      <c r="E27" s="5"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="3"/>
@@ -1575,7 +1558,7 @@
     <row r="28" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
-      <c r="E28" s="21"/>
+      <c r="E28" s="5"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="3"/>
@@ -1592,7 +1575,7 @@
     <row r="29" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
-      <c r="E29" s="21"/>
+      <c r="E29" s="5"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="3"/>
@@ -1609,7 +1592,7 @@
     <row r="30" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
-      <c r="E30" s="21"/>
+      <c r="E30" s="5"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="3"/>
@@ -1626,7 +1609,7 @@
     <row r="31" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
-      <c r="E31" s="21"/>
+      <c r="E31" s="5"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="3"/>
@@ -1643,7 +1626,7 @@
     <row r="32" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="21"/>
+      <c r="E32" s="5"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="3"/>
@@ -1660,7 +1643,7 @@
     <row r="33" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="21"/>
+      <c r="E33" s="5"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="3"/>
@@ -1677,7 +1660,7 @@
     <row r="34" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
-      <c r="E34" s="21"/>
+      <c r="E34" s="5"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="3"/>
@@ -1694,7 +1677,7 @@
     <row r="35" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
-      <c r="E35" s="21"/>
+      <c r="E35" s="5"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="3"/>
@@ -1711,7 +1694,7 @@
     <row r="36" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
-      <c r="E36" s="21"/>
+      <c r="E36" s="5"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="3"/>
@@ -1728,7 +1711,7 @@
     <row r="37" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="21"/>
+      <c r="E37" s="5"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="3"/>
@@ -1745,7 +1728,7 @@
     <row r="38" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
-      <c r="E38" s="21"/>
+      <c r="E38" s="5"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="3"/>
@@ -1762,7 +1745,7 @@
     <row r="39" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
-      <c r="E39" s="21"/>
+      <c r="E39" s="5"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="3"/>
@@ -1779,7 +1762,7 @@
     <row r="40" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
-      <c r="E40" s="21"/>
+      <c r="E40" s="5"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="3"/>
@@ -1796,7 +1779,7 @@
     <row r="41" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
-      <c r="E41" s="21"/>
+      <c r="E41" s="5"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
       <c r="I41" s="3"/>
@@ -1813,7 +1796,7 @@
     <row r="42" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
-      <c r="E42" s="21"/>
+      <c r="E42" s="5"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
       <c r="I42" s="3"/>
@@ -1830,7 +1813,7 @@
     <row r="43" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
-      <c r="E43" s="21"/>
+      <c r="E43" s="5"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="3"/>
@@ -1847,7 +1830,7 @@
     <row r="44" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
-      <c r="E44" s="21"/>
+      <c r="E44" s="5"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
       <c r="I44" s="3"/>
@@ -1864,7 +1847,7 @@
     <row r="45" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
-      <c r="E45" s="21"/>
+      <c r="E45" s="5"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
       <c r="I45" s="3"/>
@@ -1881,7 +1864,7 @@
     <row r="46" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
-      <c r="E46" s="21"/>
+      <c r="E46" s="5"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
       <c r="I46" s="3"/>
@@ -1898,7 +1881,7 @@
     <row r="47" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
-      <c r="E47" s="21"/>
+      <c r="E47" s="5"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="I47" s="3"/>
@@ -1915,7 +1898,7 @@
     <row r="48" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
-      <c r="E48" s="21"/>
+      <c r="E48" s="5"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="3"/>
@@ -1932,7 +1915,7 @@
     <row r="49" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
-      <c r="E49" s="21"/>
+      <c r="E49" s="5"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
       <c r="I49" s="3"/>
@@ -1949,7 +1932,7 @@
     <row r="50" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
-      <c r="E50" s="21"/>
+      <c r="E50" s="5"/>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="3"/>
@@ -1966,7 +1949,7 @@
     <row r="51" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
-      <c r="E51" s="21"/>
+      <c r="E51" s="5"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="3"/>
@@ -1983,7 +1966,7 @@
     <row r="52" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="21"/>
+      <c r="E52" s="5"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
       <c r="I52" s="3"/>
@@ -2000,7 +1983,7 @@
     <row r="53" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
-      <c r="E53" s="21"/>
+      <c r="E53" s="5"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
       <c r="I53" s="3"/>
@@ -2017,7 +2000,7 @@
     <row r="54" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
-      <c r="E54" s="21"/>
+      <c r="E54" s="5"/>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
       <c r="I54" s="3"/>
@@ -2034,7 +2017,7 @@
     <row r="55" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
-      <c r="E55" s="21"/>
+      <c r="E55" s="5"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
       <c r="I55" s="3"/>
@@ -2051,7 +2034,7 @@
     <row r="56" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
-      <c r="E56" s="21"/>
+      <c r="E56" s="5"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
       <c r="I56" s="3"/>
@@ -2068,7 +2051,7 @@
     <row r="57" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
-      <c r="E57" s="21"/>
+      <c r="E57" s="5"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
       <c r="I57" s="3"/>
@@ -2085,7 +2068,7 @@
     <row r="58" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
-      <c r="E58" s="21"/>
+      <c r="E58" s="5"/>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
       <c r="I58" s="3"/>
@@ -2102,7 +2085,7 @@
     <row r="59" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
-      <c r="E59" s="21"/>
+      <c r="E59" s="5"/>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
       <c r="I59" s="3"/>
@@ -2119,7 +2102,7 @@
     <row r="60" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
-      <c r="E60" s="21"/>
+      <c r="E60" s="5"/>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
       <c r="I60" s="3"/>
@@ -2136,7 +2119,7 @@
     <row r="61" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
-      <c r="E61" s="21"/>
+      <c r="E61" s="5"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="3"/>
@@ -2153,7 +2136,7 @@
     <row r="62" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
-      <c r="E62" s="21"/>
+      <c r="E62" s="5"/>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
       <c r="I62" s="3"/>
@@ -2170,7 +2153,7 @@
     <row r="63" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
-      <c r="E63" s="21"/>
+      <c r="E63" s="5"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="3"/>
@@ -2187,7 +2170,7 @@
     <row r="64" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
-      <c r="E64" s="21"/>
+      <c r="E64" s="5"/>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
       <c r="I64" s="3"/>
@@ -2204,7 +2187,7 @@
     <row r="65" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
-      <c r="E65" s="21"/>
+      <c r="E65" s="5"/>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
       <c r="I65" s="3"/>
@@ -2221,7 +2204,7 @@
     <row r="66" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
-      <c r="E66" s="21"/>
+      <c r="E66" s="5"/>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
       <c r="I66" s="3"/>
@@ -2238,7 +2221,7 @@
     <row r="67" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
-      <c r="E67" s="21"/>
+      <c r="E67" s="5"/>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
       <c r="I67" s="3"/>
@@ -2255,7 +2238,7 @@
     <row r="68" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
-      <c r="E68" s="21"/>
+      <c r="E68" s="5"/>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
       <c r="I68" s="3"/>
@@ -2272,7 +2255,7 @@
     <row r="69" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
-      <c r="E69" s="21"/>
+      <c r="E69" s="5"/>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
       <c r="I69" s="3"/>
@@ -2289,7 +2272,7 @@
     <row r="70" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
-      <c r="E70" s="21"/>
+      <c r="E70" s="5"/>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
       <c r="I70" s="3"/>
@@ -2306,7 +2289,7 @@
     <row r="71" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
-      <c r="E71" s="21"/>
+      <c r="E71" s="5"/>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
       <c r="I71" s="3"/>
@@ -2323,7 +2306,7 @@
     <row r="72" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
-      <c r="E72" s="21"/>
+      <c r="E72" s="5"/>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
       <c r="I72" s="3"/>
